--- a/data/Step2_Agent 역할 정의서_양식.xlsx
+++ b/data/Step2_Agent 역할 정의서_양식.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\1. 강의\1.4 기타\AIVLE 과정\AIVLE 시즌2\강의준비\9기\5.미프2_멀티 에이전트_운영시스템\에이블러용\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\1. 강의\1.4 기타\AIVLE 과정\AIVLE 시즌2\강의준비\9기\5.미프2_멀티 에이전트_운영시스템\실습파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443CBAEF-D366-4313-B97E-17D775A30055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDDABE6-EA40-4541-8397-CEEF7CEF06B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37563ECD-362D-43B2-A1B8-113A38767F2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{37563ECD-362D-43B2-A1B8-113A38767F2D}"/>
   </bookViews>
   <sheets>
-    <sheet name="agent1" sheetId="1" r:id="rId1"/>
+    <sheet name="Supervisor" sheetId="1" r:id="rId1"/>
+    <sheet name="Analyzer" sheetId="6" r:id="rId2"/>
+    <sheet name="Critic" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>항목</t>
   </si>
@@ -68,7 +70,156 @@
     <t>제약 조건</t>
   </si>
   <si>
+    <t>Critic Agent</t>
+  </si>
+  <si>
+    <t>LLM (gpt-4.1-mini)</t>
+  </si>
+  <si>
     <t>실패 시 리스크</t>
+  </si>
+  <si>
+    <t>Supervisor Agent</t>
+  </si>
+  <si>
+    <t>Analyzer Agent</t>
+  </si>
+  <si>
+    <t>전체 리뷰 분석 흐름을 통제하고, Critic 결과를 바탕으로 reason_code 분류, repair_directive 생성, 재시도 여부를 결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 현재 State 확인 및 다음 단계 결정
+- 실행 흐름 제어 (Analyzer → Critic → 재시도/종료)
+- 부적합 사유를 표준 reason_code로 분류
+- 재시도용 repair_directive 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 초기 실행 시 Analyzer 호출
+- Analyzer 결과 존재 시 Critic 호출
+- Critic 적합 시 종료
+- Critic 부적합 시 reason_code 분류
+- repair_directive 생성
+- 재시도 가능 여부 판단 (retry_count, max_retries 기준)
+- 재시도 시 상태 초기화 후 Analyzer 재호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- analyzer_result
+- critic_result
+- reason_code
+- repair_directive
+- retry_count
+- max_retries</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- next_agent ("analyzer" / "critic" / "end")
+- reason_code
+- repair_directive
+- retry_count (증가 가능)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 직접 속성/감성 분석 수행 금지
+- 직접 적합/부적합 판정 금지
+- reason_code는 정의된 범위 내에서만 선택
+- 흐름 제어와 정책 판단만 수행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 잘못된 reason_code 분류 시 불필요한 재시도 발생
+- repair_directive 품질이 낮으면 재분석 성능 저하
+- 재시도 정책 오류 시 비용 증가 및 루프 발생 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 리뷰에서 허용된 속성(aspect)과 각 속성의 감성(label), 근거(evidence)를 구조화하여 추출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 리뷰 원문 분석
+- 속성 추출- 속성별 감성 판단
+- evidence 생성
+- 필요 시 repair_directive를 반영해 수정된 결과 재생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 리뷰에서 언급된 속성만 추출
+- 허용 속성(보습, 가격, 향, 포장)만 사용
+- 각 속성별 label(0/1) 부여
+- 대표 evidence 1개 생성
+- 동일 aspect 중복 방지
+- dict 형식 결과 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- repair_directive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 허용 aspect 외 사용 금지
+- label은 0/1만 사용
+- 같은 aspect 중복 출력 금지
+- evidence는 리뷰 원문에서 확인 가능해야 함
+- 출력은 dict 1개만 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- aspect 누락/오추출 발생 가능
+- 감성 판단 오류 가능
+- evidence가 원문과 불일치할 수 있음
+- 형식 오류 시 후속 검수 및 저장 실패 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Analyzer의 분석 결과가 리뷰 원문과 일치하는지 검수하고 적합/부적합을 판정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review와 analyzer_result 비교 검토
+- 결과의 정확성/일치성 판단
+- verdict 및 reason 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- aspect가 리뷰 내용과 일치하는지 확인
+- label 판단이 적절한지 확인
+- evidence가 리뷰 원문에서 확인 가능한지 검토
+- 적합/부적합 판정
+- 판정 사유(reason) 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- review
+- analyzer_result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- critic_result
+{"verdict":"적합/부적합","reason":"..."}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 직접 재시도 여부 판단 금지
+- next_agent 결정 금지
+- 출력은 verdict/reason을 가진 dict 1개만 생성
+- 애매하면 보수적으로 부적합 판정 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 과도한 부적합 판정 시 재시도 증가
+- 부적합 사유가 불명확하면 Supervisor의 reason_code 분류 품질 저하
+- 잘못된 적합 판정 시 오류 결과가 그대로 저장될 수 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- analyzer_result
+{"items":[{"aspect":"...","label":0 또는 1,"evidence":"..."}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -541,55 +692,273 @@
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573C59AF-0BE8-4AD0-A12F-947CB901CAD7}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.875" style="2"/>
+    <col min="2" max="2" width="66.375" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="15.875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="99" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2735CA59-B664-48CC-BB17-F31BF19DA967}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.875" style="2"/>
+    <col min="2" max="2" width="65.375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="15.875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="6"/>
+    </row>
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -820,13 +1189,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3904B76-8706-4489-AD4F-3611FAD98AAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7C58F9D-4197-4AEE-9C96-7EEC34562141}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196399F5-336F-4579-B0C3-5F53E1772C7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8EF233-CCA9-44CA-96FB-374FFBD2859F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C7D950C-430D-4556-B3F0-1A044A767606}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EDD2438-A439-40C4-9881-83FAD470EA91}"/>
 </file>